--- a/Data Analysis/1_Data/dominance_mean_biomass_profit_2002_to_2017.xlsx
+++ b/Data Analysis/1_Data/dominance_mean_biomass_profit_2002_to_2017.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -390,6 +390,11 @@
           <t>sowndiv</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -415,6 +420,11 @@
       <c r="G2">
         <v>6</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -440,6 +450,11 @@
       <c r="G3">
         <v>3</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -465,6 +480,11 @@
       <c r="G4">
         <v>3</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -490,6 +510,11 @@
       <c r="G5">
         <v>2</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -515,6 +540,11 @@
       <c r="G6">
         <v>3</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -540,6 +570,11 @@
       <c r="G7">
         <v>2</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -565,6 +600,11 @@
       <c r="G8">
         <v>6</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -590,6 +630,11 @@
       <c r="G9">
         <v>6</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -615,6 +660,11 @@
       <c r="G10">
         <v>2</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -640,6 +690,11 @@
       <c r="G11">
         <v>2</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -665,6 +720,11 @@
       <c r="G12">
         <v>4</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -690,6 +750,11 @@
       <c r="G13">
         <v>3</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -715,6 +780,11 @@
       <c r="G14">
         <v>4</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -740,6 +810,11 @@
       <c r="G15">
         <v>1</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -765,6 +840,11 @@
       <c r="G16">
         <v>2</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -790,6 +870,11 @@
       <c r="G17">
         <v>3</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -815,6 +900,11 @@
       <c r="G18">
         <v>1</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -840,6 +930,11 @@
       <c r="G19">
         <v>2</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -865,6 +960,11 @@
       <c r="G20">
         <v>2</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -890,6 +990,11 @@
       <c r="G21">
         <v>9</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -915,6 +1020,11 @@
       <c r="G22">
         <v>4</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -940,6 +1050,11 @@
       <c r="G23">
         <v>4</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -965,6 +1080,11 @@
       <c r="G24">
         <v>1</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -990,6 +1110,11 @@
       <c r="G25">
         <v>2</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1015,6 +1140,11 @@
       <c r="G26">
         <v>3</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1040,6 +1170,11 @@
       <c r="G27">
         <v>6</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1065,6 +1200,11 @@
       <c r="G28">
         <v>1</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1090,6 +1230,11 @@
       <c r="G29">
         <v>2</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1115,6 +1260,11 @@
       <c r="G30">
         <v>6</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1140,6 +1290,11 @@
       <c r="G31">
         <v>2</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1165,6 +1320,11 @@
       <c r="G32">
         <v>4</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1190,6 +1350,11 @@
       <c r="G33">
         <v>2</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1215,6 +1380,11 @@
       <c r="G34">
         <v>2</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1240,6 +1410,11 @@
       <c r="G35">
         <v>3</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1265,6 +1440,11 @@
       <c r="G36">
         <v>2</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1290,6 +1470,11 @@
       <c r="G37">
         <v>3</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1315,6 +1500,11 @@
       <c r="G38">
         <v>9</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1340,6 +1530,11 @@
       <c r="G39">
         <v>4</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1365,6 +1560,11 @@
       <c r="G40">
         <v>2</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1390,6 +1590,11 @@
       <c r="G41">
         <v>2</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1415,6 +1620,11 @@
       <c r="G42">
         <v>4</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1440,6 +1650,11 @@
       <c r="G43">
         <v>4</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1465,6 +1680,11 @@
       <c r="G44">
         <v>3</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1490,6 +1710,11 @@
       <c r="G45">
         <v>3</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1515,6 +1740,11 @@
       <c r="G46">
         <v>6</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1540,6 +1770,11 @@
       <c r="G47">
         <v>4</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1565,6 +1800,11 @@
       <c r="G48">
         <v>2</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1590,6 +1830,11 @@
       <c r="G49">
         <v>3</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1615,6 +1860,11 @@
       <c r="G50">
         <v>2</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1640,6 +1890,11 @@
       <c r="G51">
         <v>2</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1665,6 +1920,11 @@
       <c r="G52">
         <v>3</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1690,6 +1950,11 @@
       <c r="G53">
         <v>2</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1715,6 +1980,11 @@
       <c r="G54">
         <v>9</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1740,6 +2010,11 @@
       <c r="G55">
         <v>2</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1765,6 +2040,11 @@
       <c r="G56">
         <v>2</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1790,6 +2070,11 @@
       <c r="G57">
         <v>1</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1815,6 +2100,11 @@
       <c r="G58">
         <v>2</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1840,6 +2130,11 @@
       <c r="G59">
         <v>3</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1865,6 +2160,11 @@
       <c r="G60">
         <v>2</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1890,6 +2190,11 @@
       <c r="G61">
         <v>4</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1915,6 +2220,11 @@
       <c r="G62">
         <v>2</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1940,6 +2250,11 @@
       <c r="G63">
         <v>2</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1965,6 +2280,11 @@
       <c r="G64">
         <v>1</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1990,6 +2310,11 @@
       <c r="G65">
         <v>3</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2015,6 +2340,11 @@
       <c r="G66">
         <v>3</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2040,6 +2370,11 @@
       <c r="G67">
         <v>2</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2065,6 +2400,11 @@
       <c r="G68">
         <v>2</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2090,6 +2430,11 @@
       <c r="G69">
         <v>4</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2115,6 +2460,11 @@
       <c r="G70">
         <v>3</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2140,6 +2490,11 @@
       <c r="G71">
         <v>2</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2165,6 +2520,11 @@
       <c r="G72">
         <v>6</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2190,6 +2550,11 @@
       <c r="G73">
         <v>3</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2215,6 +2580,11 @@
       <c r="G74">
         <v>4</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2240,6 +2610,11 @@
       <c r="G75">
         <v>1</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2265,6 +2640,11 @@
       <c r="G76">
         <v>3</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2290,6 +2670,11 @@
       <c r="G77">
         <v>3</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2315,6 +2700,11 @@
       <c r="G78">
         <v>3</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2340,6 +2730,11 @@
       <c r="G79">
         <v>2</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2365,6 +2760,11 @@
       <c r="G80">
         <v>4</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2390,6 +2790,11 @@
       <c r="G81">
         <v>6</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2415,6 +2820,11 @@
       <c r="G82">
         <v>4</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2440,6 +2850,11 @@
       <c r="G83">
         <v>1</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2465,6 +2880,11 @@
       <c r="G84">
         <v>2</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2490,6 +2910,11 @@
       <c r="G85">
         <v>6</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2515,6 +2940,11 @@
       <c r="G86">
         <v>6</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2540,6 +2970,11 @@
       <c r="G87">
         <v>4</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2565,6 +3000,11 @@
       <c r="G88">
         <v>3</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2590,6 +3030,11 @@
       <c r="G89">
         <v>2</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2615,6 +3060,11 @@
       <c r="G90">
         <v>4</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2640,6 +3090,11 @@
       <c r="G91">
         <v>3</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2665,6 +3120,11 @@
       <c r="G92">
         <v>2</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2690,6 +3150,11 @@
       <c r="G93">
         <v>3</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2715,6 +3180,11 @@
       <c r="G94">
         <v>2</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2740,6 +3210,11 @@
       <c r="G95">
         <v>4</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2765,6 +3240,11 @@
       <c r="G96">
         <v>2</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2790,6 +3270,11 @@
       <c r="G97">
         <v>1</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2815,6 +3300,11 @@
       <c r="G98">
         <v>3</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2840,6 +3330,11 @@
       <c r="G99">
         <v>6</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2865,6 +3360,11 @@
       <c r="G100">
         <v>4</v>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2890,6 +3390,11 @@
       <c r="G101">
         <v>6</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2915,6 +3420,11 @@
       <c r="G102">
         <v>2</v>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2940,6 +3450,11 @@
       <c r="G103">
         <v>2</v>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2965,6 +3480,11 @@
       <c r="G104">
         <v>9</v>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2990,6 +3510,11 @@
       <c r="G105">
         <v>2</v>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3015,6 +3540,11 @@
       <c r="G106">
         <v>1</v>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3040,6 +3570,11 @@
       <c r="G107">
         <v>2</v>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3065,6 +3600,11 @@
       <c r="G108">
         <v>2</v>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3090,6 +3630,11 @@
       <c r="G109">
         <v>1</v>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3115,6 +3660,11 @@
       <c r="G110">
         <v>1</v>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3140,6 +3690,11 @@
       <c r="G111">
         <v>6</v>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3165,6 +3720,11 @@
       <c r="G112">
         <v>2</v>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3190,6 +3750,11 @@
       <c r="G113">
         <v>6</v>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3215,6 +3780,11 @@
       <c r="G114">
         <v>4</v>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3240,6 +3810,11 @@
       <c r="G115">
         <v>4</v>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3265,6 +3840,11 @@
       <c r="G116">
         <v>3</v>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3290,6 +3870,11 @@
       <c r="G117">
         <v>2</v>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3315,6 +3900,11 @@
       <c r="G118">
         <v>6</v>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3340,6 +3930,11 @@
       <c r="G119">
         <v>4</v>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3365,6 +3960,11 @@
       <c r="G120">
         <v>2</v>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3390,6 +3990,11 @@
       <c r="G121">
         <v>6</v>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3415,6 +4020,11 @@
       <c r="G122">
         <v>9</v>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3440,6 +4050,11 @@
       <c r="G123">
         <v>3</v>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3465,6 +4080,11 @@
       <c r="G124">
         <v>2</v>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3490,6 +4110,11 @@
       <c r="G125">
         <v>4</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3515,6 +4140,11 @@
       <c r="G126">
         <v>3</v>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3540,6 +4170,11 @@
       <c r="G127">
         <v>3</v>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3565,6 +4200,11 @@
       <c r="G128">
         <v>2</v>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3590,6 +4230,11 @@
       <c r="G129">
         <v>2</v>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3615,6 +4260,11 @@
       <c r="G130">
         <v>4</v>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3640,6 +4290,11 @@
       <c r="G131">
         <v>2</v>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3665,6 +4320,11 @@
       <c r="G132">
         <v>2</v>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3690,6 +4350,11 @@
       <c r="G133">
         <v>1</v>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3715,6 +4380,11 @@
       <c r="G134">
         <v>3</v>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3740,6 +4410,11 @@
       <c r="G135">
         <v>6</v>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3765,6 +4440,11 @@
       <c r="G136">
         <v>2</v>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3790,6 +4470,11 @@
       <c r="G137">
         <v>4</v>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3815,6 +4500,11 @@
       <c r="G138">
         <v>2</v>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3840,6 +4530,11 @@
       <c r="G139">
         <v>2</v>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3865,6 +4560,11 @@
       <c r="G140">
         <v>3</v>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3890,6 +4590,11 @@
       <c r="G141">
         <v>4</v>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3915,6 +4620,11 @@
       <c r="G142">
         <v>3</v>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3940,6 +4650,11 @@
       <c r="G143">
         <v>3</v>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3965,6 +4680,11 @@
       <c r="G144">
         <v>4</v>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3990,6 +4710,11 @@
       <c r="G145">
         <v>4</v>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4015,6 +4740,11 @@
       <c r="G146">
         <v>2</v>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4040,6 +4770,11 @@
       <c r="G147">
         <v>3</v>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4065,6 +4800,11 @@
       <c r="G148">
         <v>3</v>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4090,6 +4830,11 @@
       <c r="G149">
         <v>2</v>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4115,6 +4860,11 @@
       <c r="G150">
         <v>9</v>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4140,6 +4890,11 @@
       <c r="G151">
         <v>2</v>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4165,6 +4920,11 @@
       <c r="G152">
         <v>3</v>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4190,6 +4950,11 @@
       <c r="G153">
         <v>6</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4215,6 +4980,11 @@
       <c r="G154">
         <v>2</v>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4240,6 +5010,11 @@
       <c r="G155">
         <v>3</v>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4265,6 +5040,11 @@
       <c r="G156">
         <v>2</v>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4290,6 +5070,11 @@
       <c r="G157">
         <v>2</v>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4315,6 +5100,11 @@
       <c r="G158">
         <v>3</v>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4340,6 +5130,11 @@
       <c r="G159">
         <v>2</v>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4365,6 +5160,11 @@
       <c r="G160">
         <v>2</v>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4390,6 +5190,11 @@
       <c r="G161">
         <v>9</v>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4415,6 +5220,11 @@
       <c r="G162">
         <v>2</v>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4440,6 +5250,11 @@
       <c r="G163">
         <v>2</v>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4465,6 +5280,11 @@
       <c r="G164">
         <v>2</v>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4490,6 +5310,11 @@
       <c r="G165">
         <v>2</v>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4515,6 +5340,11 @@
       <c r="G166">
         <v>2</v>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4540,6 +5370,11 @@
       <c r="G167">
         <v>2</v>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4565,6 +5400,11 @@
       <c r="G168">
         <v>3</v>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4590,6 +5430,11 @@
       <c r="G169">
         <v>4</v>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4615,6 +5460,11 @@
       <c r="G170">
         <v>2</v>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4640,6 +5490,11 @@
       <c r="G171">
         <v>2</v>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4665,6 +5520,11 @@
       <c r="G172">
         <v>3</v>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4690,6 +5550,11 @@
       <c r="G173">
         <v>4</v>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4715,6 +5580,11 @@
       <c r="G174">
         <v>6</v>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4740,6 +5610,11 @@
       <c r="G175">
         <v>4</v>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4765,6 +5640,11 @@
       <c r="G176">
         <v>3</v>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4790,6 +5670,11 @@
       <c r="G177">
         <v>2</v>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4815,6 +5700,11 @@
       <c r="G178">
         <v>1</v>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4840,6 +5730,11 @@
       <c r="G179">
         <v>3</v>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4865,6 +5760,11 @@
       <c r="G180">
         <v>2</v>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4890,6 +5790,11 @@
       <c r="G181">
         <v>3</v>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4915,6 +5820,11 @@
       <c r="G182">
         <v>2</v>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4940,6 +5850,11 @@
       <c r="G183">
         <v>3</v>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4965,6 +5880,11 @@
       <c r="G184">
         <v>1</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4990,6 +5910,11 @@
       <c r="G185">
         <v>2</v>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5015,6 +5940,11 @@
       <c r="G186">
         <v>1</v>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5040,6 +5970,11 @@
       <c r="G187">
         <v>6</v>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5065,6 +6000,11 @@
       <c r="G188">
         <v>3</v>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5090,6 +6030,11 @@
       <c r="G189">
         <v>1</v>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5115,6 +6060,11 @@
       <c r="G190">
         <v>2</v>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5140,6 +6090,11 @@
       <c r="G191">
         <v>3</v>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5165,6 +6120,11 @@
       <c r="G192">
         <v>4</v>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5190,6 +6150,11 @@
       <c r="G193">
         <v>4</v>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5215,6 +6180,11 @@
       <c r="G194">
         <v>4</v>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5240,6 +6210,11 @@
       <c r="G195">
         <v>2</v>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5265,6 +6240,11 @@
       <c r="G196">
         <v>4</v>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5290,6 +6270,11 @@
       <c r="G197">
         <v>4</v>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5315,6 +6300,11 @@
       <c r="G198">
         <v>9</v>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5340,6 +6330,11 @@
       <c r="G199">
         <v>6</v>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5365,6 +6360,11 @@
       <c r="G200">
         <v>3</v>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5390,6 +6390,11 @@
       <c r="G201">
         <v>6</v>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5415,6 +6420,11 @@
       <c r="G202">
         <v>3</v>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5440,6 +6450,11 @@
       <c r="G203">
         <v>1</v>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5465,6 +6480,11 @@
       <c r="G204">
         <v>3</v>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5490,6 +6510,11 @@
       <c r="G205">
         <v>6</v>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5515,6 +6540,11 @@
       <c r="G206">
         <v>4</v>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5539,6 +6569,11 @@
       </c>
       <c r="G207">
         <v>6</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
       </c>
     </row>
   </sheetData>
